--- a/excel/操作.xlsx
+++ b/excel/操作.xlsx
@@ -1281,6 +1281,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1391,23 +1392,24 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="246871552"/>
-        <c:axId val="246873472"/>
+        <c:axId val="266925568"/>
+        <c:axId val="266927488"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="246871552"/>
+        <c:axId val="266925568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="246873472"/>
+        <c:crossAx val="266927488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1415,7 +1417,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="246873472"/>
+        <c:axId val="266927488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -1425,6 +1427,7 @@
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:txPr>
             <a:bodyPr rot="0" vert="wordArtVertRtl"/>
@@ -1441,13 +1444,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="246871552"/>
+        <c:crossAx val="266925568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -1492,6 +1496,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1583,8 +1588,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="247187328"/>
-        <c:axId val="247188864"/>
+        <c:axId val="267241344"/>
+        <c:axId val="267242880"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="stacked"/>
@@ -1666,11 +1671,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="247466624"/>
-        <c:axId val="247465088"/>
+        <c:axId val="267254400"/>
+        <c:axId val="267252864"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="247187328"/>
+        <c:axId val="267241344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1679,7 +1684,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="247188864"/>
+        <c:crossAx val="267242880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1687,7 +1692,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="247188864"/>
+        <c:axId val="267242880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1698,12 +1703,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="247187328"/>
+        <c:crossAx val="267241344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="247465088"/>
+        <c:axId val="267252864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1713,12 +1718,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="247466624"/>
+        <c:crossAx val="267254400"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="247466624"/>
+        <c:axId val="267254400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1727,7 +1732,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="247465088"/>
+        <c:crossAx val="267252864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1737,6 +1742,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -4807,7 +4813,7 @@
       </c>
       <c r="B160" s="18">
         <f ca="1">NOW()</f>
-        <v>43775.008437384262</v>
+        <v>43775.157350578702</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.15">
